--- a/Microsoft_Office_Specialist_Associate/02-Excel/Aula08/Eficiencia.xlsx
+++ b/Microsoft_Office_Specialist_Associate/02-Excel/Aula08/Eficiencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Documents\GitHub\SENAI2025_Luis\Microsoft_Office_Specialist_Associate\02-Excel\Aula08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBDB7D17-F7A0-43C4-AAA9-9BDF7846B5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E60980-4DA9-4CB5-84D9-6A1DA9A59839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{5ED1698B-09E0-45C3-B9B4-186622A85249}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{5ED1698B-09E0-45C3-B9B4-186622A85249}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -913,23 +913,23 @@
       </c>
       <c r="C4">
         <f ca="1">RANDBETWEEN(25000,30000)</f>
-        <v>29758</v>
+        <v>28242</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:G5" ca="1" si="0">RANDBETWEEN(25000,30000)</f>
-        <v>27247</v>
+        <v>25644</v>
       </c>
       <c r="E4">
         <f ca="1">RANDBETWEEN(25000,30000)</f>
-        <v>26388</v>
+        <v>26930</v>
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="0"/>
-        <v>25749</v>
+        <v>25487</v>
       </c>
       <c r="G4">
         <f t="shared" ca="1" si="0"/>
-        <v>27334</v>
+        <v>27125</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -938,23 +938,23 @@
       </c>
       <c r="C5">
         <f ca="1">RANDBETWEEN(25000,30000)</f>
-        <v>27057</v>
+        <v>29401</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>29568</v>
+        <v>28092</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="0"/>
-        <v>25992</v>
+        <v>27100</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="0"/>
-        <v>27360</v>
+        <v>27449</v>
       </c>
       <c r="G5">
         <f t="shared" ca="1" si="0"/>
-        <v>29896</v>
+        <v>26261</v>
       </c>
     </row>
   </sheetData>
